--- a/data-source/可升级建筑数据.xlsx
+++ b/data-source/可升级建筑数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A2922B-B5D7-42A3-998B-7B86D1DC67F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C944E7A-0104-4C80-9F4D-7E3F751DE3D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{9A7D2943-CAC0-4F21-9EB5-FAC98526D314}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="169">
   <si>
     <t>建筑名称</t>
   </si>
@@ -661,6 +661,27 @@
   </si>
   <si>
     <t>非城堡建筑</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>一次性制作20个食物</t>
+  </si>
+  <si>
+    <t>一次性制作40个食物</t>
+  </si>
+  <si>
+    <t>一次性制作60个食物</t>
+  </si>
+  <si>
+    <t>一次性制作80个食物</t>
+  </si>
+  <si>
+    <t>原松木*3；石灰岩*3；亚麻纤维*1</t>
+  </si>
+  <si>
+    <t>松木板*60；石灰岩*60；桦木板*40；炉架*20；煤炭*20；山毛榉*20；U形钉*20；岩盐*20</t>
   </si>
 </sst>
 </file>
@@ -767,11 +788,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1110,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F3F2D7E-6F72-42A4-A4D4-224A41E11217}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.53125" customWidth="1"/>
@@ -1158,7 +1179,7 @@
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="6">
@@ -1190,7 +1211,7 @@
       <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="27" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="6"/>
       <c r="C3" s="3" t="s">
         <v>76</v>
@@ -1204,7 +1225,7 @@
       <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>63</v>
       </c>
       <c r="H3" s="6"/>
@@ -1216,7 +1237,7 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="6"/>
       <c r="C4" s="3" t="s">
         <v>77</v>
@@ -1230,7 +1251,7 @@
       <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="7"/>
+      <c r="G4" s="8"/>
       <c r="H4" s="6"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1240,7 +1261,7 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="6"/>
       <c r="C5" s="3" t="s">
         <v>78</v>
@@ -1254,7 +1275,7 @@
       <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="7"/>
+      <c r="G5" s="8"/>
       <c r="H5" s="6"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -1264,7 +1285,7 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="6">
@@ -1296,7 +1317,7 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="6"/>
       <c r="C7" s="3" t="s">
         <v>76</v>
@@ -1310,7 +1331,7 @@
       <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>63</v>
       </c>
       <c r="H7" s="6"/>
@@ -1322,7 +1343,7 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="7"/>
       <c r="B8" s="6"/>
       <c r="C8" s="3" t="s">
         <v>77</v>
@@ -1336,7 +1357,7 @@
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="7"/>
+      <c r="G8" s="8"/>
       <c r="H8" s="6"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1346,7 +1367,7 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="6"/>
       <c r="C9" s="3" t="s">
         <v>78</v>
@@ -1360,7 +1381,7 @@
       <c r="F9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="7"/>
+      <c r="G9" s="8"/>
       <c r="H9" s="6"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1370,7 +1391,7 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="6">
@@ -1402,7 +1423,7 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="6"/>
       <c r="C11" s="3" t="s">
         <v>76</v>
@@ -1416,7 +1437,7 @@
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>63</v>
       </c>
       <c r="H11" s="6"/>
@@ -1428,7 +1449,7 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
+      <c r="A12" s="7"/>
       <c r="B12" s="6"/>
       <c r="C12" s="3" t="s">
         <v>77</v>
@@ -1442,7 +1463,7 @@
       <c r="F12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="7"/>
+      <c r="G12" s="8"/>
       <c r="H12" s="6"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1452,7 +1473,7 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
+      <c r="A13" s="7"/>
       <c r="B13" s="6"/>
       <c r="C13" s="3" t="s">
         <v>78</v>
@@ -1466,7 +1487,7 @@
       <c r="F13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="7"/>
+      <c r="G13" s="8"/>
       <c r="H13" s="6"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1476,7 +1497,7 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="6">
@@ -1508,7 +1529,7 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="6"/>
       <c r="C15" s="3" t="s">
         <v>76</v>
@@ -1522,7 +1543,7 @@
       <c r="F15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>63</v>
       </c>
       <c r="H15" s="6"/>
@@ -1534,7 +1555,7 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="7"/>
       <c r="B16" s="6"/>
       <c r="C16" s="3" t="s">
         <v>77</v>
@@ -1548,7 +1569,7 @@
       <c r="F16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="7"/>
+      <c r="G16" s="8"/>
       <c r="H16" s="6"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1558,7 +1579,7 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
+      <c r="A17" s="7"/>
       <c r="B17" s="6"/>
       <c r="C17" s="3" t="s">
         <v>78</v>
@@ -1572,7 +1593,7 @@
       <c r="F17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="7"/>
+      <c r="G17" s="8"/>
       <c r="H17" s="6"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1582,7 +1603,7 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="6">
@@ -1614,7 +1635,7 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
+      <c r="A19" s="7"/>
       <c r="B19" s="6"/>
       <c r="C19" s="3" t="s">
         <v>76</v>
@@ -1628,7 +1649,7 @@
       <c r="F19" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>63</v>
       </c>
       <c r="H19" s="6"/>
@@ -1640,7 +1661,7 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
+      <c r="A20" s="7"/>
       <c r="B20" s="6"/>
       <c r="C20" s="3" t="s">
         <v>77</v>
@@ -1654,7 +1675,7 @@
       <c r="F20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="7"/>
+      <c r="G20" s="8"/>
       <c r="H20" s="6"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1664,7 +1685,7 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
+      <c r="A21" s="7"/>
       <c r="B21" s="6"/>
       <c r="C21" s="3" t="s">
         <v>78</v>
@@ -1678,7 +1699,7 @@
       <c r="F21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="7"/>
+      <c r="G21" s="8"/>
       <c r="H21" s="6"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1687,24 +1708,24 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" ht="27" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>47</v>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B22" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D22" s="1">
-        <v>200</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>48</v>
+        <v>10</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>15</v>
@@ -1712,9 +1733,7 @@
       <c r="H22" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>53</v>
-      </c>
+      <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1722,77 +1741,73 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" ht="27" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
+      <c r="A23" s="7"/>
       <c r="B23" s="6"/>
       <c r="C23" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D23" s="1">
-        <v>500</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>54</v>
+        <v>168</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="H23" s="6"/>
-      <c r="I23" s="7"/>
+      <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" ht="27" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="7"/>
       <c r="B24" s="6"/>
       <c r="C24" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D24" s="1">
-        <v>1000</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>54</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="8"/>
       <c r="H24" s="6"/>
-      <c r="I24" s="7"/>
+      <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" ht="27" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
+    <row r="25" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7"/>
       <c r="B25" s="6"/>
       <c r="C25" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D25" s="1">
-        <v>1700</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>57</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="8"/>
       <c r="H25" s="6"/>
-      <c r="I25" s="7"/>
+      <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1801,7 +1816,7 @@
     </row>
     <row r="26" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B26" s="6">
         <v>1</v>
@@ -1813,7 +1828,7 @@
         <v>200</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>55</v>
@@ -1825,7 +1840,7 @@
         <v>17</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -1843,16 +1858,16 @@
         <v>500</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H27" s="6"/>
-      <c r="I27" s="7"/>
+      <c r="I27" s="8"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1869,16 +1884,16 @@
         <v>1000</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H28" s="6"/>
-      <c r="I28" s="7"/>
+      <c r="I28" s="8"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1895,25 +1910,25 @@
         <v>1700</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>57</v>
       </c>
       <c r="H29" s="6"/>
-      <c r="I29" s="7"/>
+      <c r="I29" s="8"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B30" s="6">
         <v>1</v>
@@ -1925,18 +1940,20 @@
         <v>200</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I30" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="31" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
@@ -1945,17 +1962,19 @@
         <v>76</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="H31" s="6"/>
-      <c r="I31" s="1"/>
+      <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
@@ -1964,17 +1983,19 @@
         <v>77</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="G32" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="H32" s="6"/>
-      <c r="I32" s="1"/>
+      <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
@@ -1983,42 +2004,44 @@
         <v>78</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G33" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="H33" s="6"/>
-      <c r="I33" s="1"/>
+      <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B34" s="6">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>15</v>
+        <v>67</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="I34" s="1"/>
     </row>
@@ -2026,20 +2049,18 @@
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D35" s="1">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="1"/>
     </row>
@@ -2047,20 +2068,18 @@
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D36" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>54</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="1"/>
     </row>
@@ -2068,69 +2087,67 @@
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D37" s="1">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>54</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
+      <c r="A38" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="6">
+        <v>1</v>
+      </c>
       <c r="C38" s="3" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="D38" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B39" s="6">
-        <v>1</v>
-      </c>
+    <row r="39" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
       <c r="C39" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D39" s="1">
-        <v>300</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>96</v>
+        <v>500</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H39" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="H39" s="6"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.3">
@@ -2140,37 +2157,37 @@
         <v>76</v>
       </c>
       <c r="D40" s="1">
-        <v>800</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>94</v>
+        <v>2000</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D41" s="1">
-        <v>1500</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>16</v>
+        <v>3000</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>16</v>
+        <v>84</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="1"/>
@@ -2182,15 +2199,15 @@
         <v>78</v>
       </c>
       <c r="D42" s="1">
-        <v>2500</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>16</v>
+        <v>4000</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H42" s="6"/>
@@ -2198,28 +2215,28 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B43" s="6">
         <v>1</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>99</v>
+        <v>300</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="I43" s="1"/>
     </row>
@@ -2227,40 +2244,40 @@
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D44" s="1">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>99</v>
+        <v>158</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D45" s="1">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="1"/>
@@ -2269,553 +2286,699 @@
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D46" s="1">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
+      <c r="A47" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="6">
+        <v>1</v>
+      </c>
       <c r="C47" s="3" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="D47" s="1">
-        <v>2000</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>103</v>
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H47" s="6"/>
+        <v>106</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B48" s="6">
-        <v>1</v>
-      </c>
+    <row r="48" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
       <c r="C48" s="3" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>56</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H48" s="6"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D49" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G49" s="6"/>
+        <v>107</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="H49" s="6"/>
       <c r="I49" s="1"/>
     </row>
-    <row r="50" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D50" s="1">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G50" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="H50" s="6"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D51" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G51" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="H51" s="6"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
+      <c r="A52" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="6">
+        <v>1</v>
+      </c>
       <c r="C52" s="3" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="D52" s="1">
-        <v>2000</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="I52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B53" s="6">
-        <v>1</v>
-      </c>
+    <row r="53" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
       <c r="C53" s="3" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>56</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D54" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="1"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D55" s="1">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D56" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
+      <c r="A57" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" s="6">
+        <v>1</v>
+      </c>
       <c r="C57" s="3" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="D57" s="1">
-        <v>2000</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A58" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B58" s="6">
-        <v>1</v>
-      </c>
+    <row r="58" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
       <c r="C58" s="3" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D58" s="1">
-        <v>0</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>56</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
       <c r="I58" s="1"/>
     </row>
-    <row r="59" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D59" s="1">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="G59" s="6"/>
       <c r="H59" s="6"/>
       <c r="I59" s="1"/>
     </row>
-    <row r="60" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
+    <row r="60" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+      <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D60" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="G60" s="6"/>
       <c r="H60" s="6"/>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D61" s="1">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="6"/>
+      <c r="A62" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="6">
+        <v>1</v>
+      </c>
       <c r="C62" s="3" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="D62" s="1">
-        <v>1600</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>140</v>
+        <v>0</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H62" s="6"/>
+        <v>130</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B63" s="6">
-        <v>1</v>
-      </c>
+    <row r="63" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A63" s="7"/>
+      <c r="B63" s="6"/>
       <c r="C63" s="3" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>56</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H63" s="6"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="A64" s="6"/>
+    <row r="64" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A64" s="7"/>
       <c r="B64" s="6"/>
       <c r="C64" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D64" s="1">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>132</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G64" s="6"/>
+        <v>139</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="H64" s="6"/>
       <c r="I64" s="1"/>
     </row>
-    <row r="65" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
+    <row r="65" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A65" s="7"/>
       <c r="B65" s="6"/>
       <c r="C65" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D65" s="1">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G65" s="6"/>
+        <v>141</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="H65" s="6"/>
       <c r="I65" s="1"/>
     </row>
-    <row r="66" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="A66" s="6"/>
+    <row r="66" spans="1:9" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A66" s="7"/>
       <c r="B66" s="6"/>
       <c r="C66" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D66" s="1">
-        <v>2600</v>
+        <v>1600</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>134</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G66" s="6"/>
+        <v>140</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="H66" s="6"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
+    <row r="67" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B67" s="6">
+        <v>1</v>
+      </c>
       <c r="C67" s="3" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="D67" s="1">
-        <v>3400</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="I67" s="1"/>
     </row>
     <row r="68" spans="1:9" ht="27" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>156</v>
-      </c>
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
       <c r="C68" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>155</v>
+      <c r="D68" s="1">
+        <v>2000</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>161</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
-      <c r="B69" s="7"/>
+      <c r="B69" s="6"/>
       <c r="C69" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D69" s="6"/>
+      <c r="D69" s="1">
+        <v>2200</v>
+      </c>
       <c r="E69" s="1" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
-      <c r="B70" s="7"/>
+      <c r="B70" s="6"/>
       <c r="C70" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D70" s="6"/>
+      <c r="D70" s="1">
+        <v>2600</v>
+      </c>
       <c r="E70" s="1" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="G70" s="6"/>
       <c r="H70" s="6"/>
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
-      <c r="B71" s="7"/>
+      <c r="B71" s="6"/>
       <c r="C71" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D71" s="6"/>
+      <c r="D71" s="1">
+        <v>3400</v>
+      </c>
       <c r="E71" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G71" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="G71" s="6"/>
       <c r="H71" s="6"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="H72" s="5"/>
+    <row r="72" spans="1:9" ht="27" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="6"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D73" s="6"/>
+      <c r="E73" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" s="6"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="6"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D74" s="6"/>
+      <c r="E74" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" s="6"/>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="6"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D75" s="6"/>
+      <c r="E75" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" s="6"/>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H76" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="64">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="D72:D75"/>
+    <mergeCell ref="H72:H75"/>
+    <mergeCell ref="H52:H56"/>
+    <mergeCell ref="H57:H61"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="H62:H66"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="G67:G71"/>
+    <mergeCell ref="H67:H71"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="G52:G56"/>
+    <mergeCell ref="G57:G61"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="G34:G37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="H38:H42"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="H47:H51"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="H43:H46"/>
+    <mergeCell ref="I26:I29"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="I30:I33"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="A14:A17"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="G3:G5"/>
@@ -2824,58 +2987,6 @@
     <mergeCell ref="H6:H9"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="H14:H17"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H18:H21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="I22:I25"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="I26:I29"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="A43:A47"/>
-    <mergeCell ref="B43:B47"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="H39:H42"/>
-    <mergeCell ref="B53:B57"/>
-    <mergeCell ref="G48:G52"/>
-    <mergeCell ref="G53:G57"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="G30:G33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="D68:D71"/>
-    <mergeCell ref="H68:H71"/>
-    <mergeCell ref="H48:H52"/>
-    <mergeCell ref="H53:H57"/>
-    <mergeCell ref="B58:B62"/>
-    <mergeCell ref="A58:A62"/>
-    <mergeCell ref="H58:H62"/>
-    <mergeCell ref="B63:B67"/>
-    <mergeCell ref="G63:G67"/>
-    <mergeCell ref="H63:H67"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="A48:A52"/>
-    <mergeCell ref="A53:A57"/>
-    <mergeCell ref="B48:B52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
